--- a/Templates/MWSS with Submersible Pump.xlsx
+++ b/Templates/MWSS with Submersible Pump.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20325"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{B8B4F913-D02E-416E-A0DD-0845709C7A35}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -95,12 +89,15 @@
   </si>
   <si>
     <t>Providing and laying in position cement concrete of specified grade excluding the cost of centering and shuttering - All work up to plinth level: 1:2:4 )1 cement : 2 coarse sand : 4 graded stone aggregate 40 mm nominal size) (Code: 4.1.4)</t>
+  </si>
+  <si>
+    <t>Installation of Single Phase Panel board where new electricity connection is required (Excluding Motor Starter) (Code: GWDDR363)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -225,7 +222,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -277,7 +274,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -471,22 +468,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7160FCE5-4C60-4FD1-9EF6-B79422E2B9A5}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="31.7265625" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -494,7 +491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -502,7 +499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -510,7 +507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -518,7 +515,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -526,7 +523,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -534,7 +531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -542,7 +539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -550,7 +547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -558,7 +555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -566,123 +563,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="87" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="135" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="116" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="2">
         <v>3000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B18" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="255" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="217.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B23" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+    <row r="24" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B24" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+    <row r="25" spans="1:2" ht="116" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B25" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+    <row r="26" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B26" s="2">
         <v>4</v>
       </c>
     </row>

--- a/Templates/MWSS with Submersible Pump.xlsx
+++ b/Templates/MWSS with Submersible Pump.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20325"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{0E414F90-9249-4889-9541-111E75EDCFBF}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -92,13 +98,31 @@
   </si>
   <si>
     <t>Installation of Single Phase Panel board where new electricity connection is required (Excluding Motor Starter) (Code: GWDDR363)</t>
+  </si>
+  <si>
+    <t>Pump &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Electrification</t>
+  </si>
+  <si>
+    <t>Civil Structures</t>
+  </si>
+  <si>
+    <t>Water Tank &amp; Fittings</t>
+  </si>
+  <si>
+    <t>Pumping &amp; Distribution Network</t>
+  </si>
+  <si>
+    <t>Supplementory Works</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -106,6 +130,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -121,7 +153,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -144,11 +176,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -161,6 +219,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,22 +532,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.7265625" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.1796875" style="1"/>
+    <col min="1" max="1" width="31.7109375" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -491,79 +555,75 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6"/>
+    </row>
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="130.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="135" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="6"/>
+    </row>
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -571,7 +631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="87" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -579,119 +639,167 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="116" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B18" s="2">
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B24" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B25" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="26" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B26" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="27" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B27" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="217.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:2" ht="255" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B30" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="116" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="31" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B31" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="32" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B32" s="2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Templates/MWSS with Submersible Pump.xlsx
+++ b/Templates/MWSS with Submersible Pump.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{0E414F90-9249-4889-9541-111E75EDCFBF}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{81C49207-BB84-4550-86DC-C8C2810763F3}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -55,9 +55,6 @@
     <t>S &amp; F Motor starters of the following ratings Submersible pump controllers with ammeter,DPMCB for single phase 2 HP submersible motor pumps (DOL) (90.14.28.13) (Code: GWDDR134)</t>
   </si>
   <si>
-    <t>Estimate For Fabricated Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 4 m Height (Code: GWDDR003)</t>
-  </si>
-  <si>
     <t>Providing and placing on terrace (at all floor levels) polyethylene water storage tank :ISI 12701 marked, with cover and suitable locking arrangement and making necessary holes for inlet, outlet and overflow pipes but without fittings and the base support for tank. (Code: 18.48)</t>
   </si>
   <si>
@@ -73,15 +70,6 @@
     <t>PVC Ball valve 50 mm (Code: GWDMR043)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 10Kgf/cm2 (50.18.9.6.1) (Code: GWDDR192)</t>
-  </si>
-  <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge 40 mm dia 10Kgf/cm2 (50.18.9.5.1) (Code: GWDDR190)</t>
-  </si>
-  <si>
-    <t>Providing and fixing PVC pipes includings jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.32 mm dia 10.Kgf/cm2 (50.18.9.4.1) (Code: GWDDR188)</t>
-  </si>
-  <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 25 mm dia 10KGF/cm2 (50.18.9.3.2) (Code: GWDDR187)</t>
   </si>
   <si>
@@ -116,18 +104,50 @@
   </si>
   <si>
     <t>Supplementory Works</t>
+  </si>
+  <si>
+    <t>Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 4 m Height (Code: GWDDR003)</t>
+  </si>
+  <si>
+    <t>GI Bend 40 mm (Code: GWDMR053)</t>
+  </si>
+  <si>
+    <t>GI Socket 40 mm (Code: GWDMR057)</t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 50 mm dia 10Kgf/cm2 (50.18.9.6.1) (Code: GWDDR192)</t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching refilling &amp; testing of joints complete as per direction of Engineer in Charge 40 mm dia 10Kgf/cm2 (50.18.9.5.1) (Code: GWDDR190)</t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.32 mm dia 10.Kgf/cm2 (50.18.9.4.1) (Code: GWDDR188)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -206,24 +226,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -286,7 +315,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -338,7 +367,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -540,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.7109375" style="4" customWidth="1"/>
@@ -556,10 +585,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="6"/>
+      <c r="A2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -601,107 +630,107 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="75" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="105" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:2" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="B20" s="2">
         <v>3000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
@@ -709,37 +738,37 @@
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="2">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="9"/>
     </row>
     <row r="26" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B26" s="2">
         <v>50</v>
@@ -747,58 +776,74 @@
     </row>
     <row r="27" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" spans="1:2" ht="255" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="2">
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="9"/>
+    </row>
+    <row r="32" spans="1:2" ht="255" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="2">
+    <row r="33" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="120" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="2">
+    <row r="34" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="2">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Templates/MWSS with Submersible Pump.xlsx
+++ b/Templates/MWSS with Submersible Pump.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20325"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Core i5 GAMING\Desktop\estimate-drafter\Templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{81C49207-BB84-4550-86DC-C8C2810763F3}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Flushing (Developing) Borewell (Code: GWDDR105)</t>
   </si>
@@ -122,12 +116,15 @@
   </si>
   <si>
     <t>Providing and fixing PVC pipes including jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge.32 mm dia 10.Kgf/cm2 (50.18.9.4.1) (Code: GWDDR188)</t>
+  </si>
+  <si>
+    <t>KSEB Charges</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -315,7 +312,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -367,7 +364,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -561,22 +558,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="31.7265625" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -584,13 +581,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="9"/>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -598,7 +595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -606,7 +603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -614,7 +611,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="130.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -622,7 +619,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -630,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
@@ -638,7 +635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
@@ -646,7 +643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="72.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
@@ -654,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -662,13 +659,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="9"/>
     </row>
-    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
@@ -676,7 +673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="87" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
@@ -684,13 +681,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="9"/>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
@@ -698,7 +695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
@@ -706,7 +703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -714,13 +711,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="9"/>
     </row>
-    <row r="20" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="116" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -728,7 +725,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
@@ -736,7 +733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
@@ -744,7 +741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
@@ -752,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>15</v>
       </c>
@@ -760,13 +757,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="9"/>
     </row>
-    <row r="26" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
@@ -774,7 +771,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
@@ -782,7 +779,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>33</v>
       </c>
@@ -790,7 +787,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>16</v>
       </c>
@@ -798,7 +795,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
@@ -806,13 +803,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="1:2" ht="255" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="217.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>17</v>
       </c>
@@ -820,7 +817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="116" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>19</v>
       </c>
@@ -828,12 +825,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="101.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="2">
         <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
